--- a/Cảm biến + Sim.xlsx
+++ b/Cảm biến + Sim.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/43e69fe3b798304f/Work/PIO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_F25DC773A252ABDACC104887E15F42345ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B63D6255-6C2C-4CBD-A136-B91A8B6B4C09}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="11_F25DC773A252ABDACC104887E15F42345ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7E32509-3FBB-4B93-90C9-0C7062858195}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="5868" windowWidth="22332" windowHeight="10632" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4428" yWindow="1752" windowWidth="22332" windowHeight="12516" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -82,9 +82,6 @@
     <t>12D20S</t>
   </si>
   <si>
-    <t>Bờ kè 3</t>
-  </si>
-  <si>
     <t>01699517089</t>
   </si>
   <si>
@@ -155,6 +152,9 @@
   </si>
   <si>
     <t>01698049699</t>
+  </si>
+  <si>
+    <t>Kênh 12</t>
   </si>
 </sst>
 </file>
@@ -277,6 +277,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -596,7 +600,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4198199E-6EFB-4E2F-AA15-45E6757C4120}">
-  <dimension ref="B2:F17"/>
+  <dimension ref="B2:M17"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.296875" customWidth="1"/>
@@ -606,7 +610,7 @@
     <col min="6" max="6" width="15.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>8</v>
       </c>
@@ -620,7 +624,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>9</v>
       </c>
@@ -634,7 +638,7 @@
         <v>46011</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>12</v>
       </c>
@@ -648,26 +652,29 @@
         <v>46078</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3">
-        <v>46208</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="D5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="10">
+        <v>46573</v>
+      </c>
+      <c r="F5" s="11">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>14</v>
@@ -679,12 +686,12 @@
         <v>20000</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>14</v>
@@ -693,12 +700,12 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>14</v>
@@ -707,12 +714,12 @@
         <v>46068</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>14</v>
@@ -721,12 +728,12 @@
         <v>46099</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>14</v>
@@ -735,20 +742,20 @@
         <v>46313</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C11" s="4" t="s">
+    </row>
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
       <c r="C12" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>14</v>
@@ -757,15 +764,15 @@
         <v>46374</v>
       </c>
       <c r="F12" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+      <c r="C13" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>14</v>
@@ -774,15 +781,15 @@
         <v>46374</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>14</v>
@@ -790,13 +797,16 @@
       <c r="E14" s="3">
         <v>46078</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="M14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>11</v>
@@ -805,12 +815,12 @@
         <v>46588</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="3:3" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C17" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
